--- a/output/affiliators_jelajahi.xlsx
+++ b/output/affiliators_jelajahi.xlsx
@@ -496,19 +496,19 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>creator_74963042</t>
+          <t>creator_74950919</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>azisfandoipFurnitur</t>
+          <t>sepandangFashion Muslim</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2129600</v>
+        <v>28100</v>
       </c>
       <c r="D2" t="n">
-        <v>1000000</v>
+        <v>11000000</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -519,11 +519,7 @@
       <c r="G2" t="n">
         <v>0</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>+62343544455455</t>
-        </is>
-      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
         <v>0</v>
@@ -539,12 +535,12 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>https://affiliate-id.tokopedia.com/connection/creator/detail?cid=7496304204793612370&amp;pair_source=author_recommend&amp;enter_from=affiliate_find_creators&amp;search_key=moLrQqnYOmc9rdb5vGEpMAVlRq7yu6mi5ces3EQr6Ak%3D&amp;req_id=2026042320331242571D4EDEC0B302BD94&amp;query=&amp;shop_region=ID&amp;shop_id=7495177173399997259</t>
+          <t>https://affiliate-id.tokopedia.com/connection/creator/detail?cid=7495091977829977029&amp;pair_source=author_recommend&amp;enter_from=affiliate_find_creators&amp;search_key=Wv1EapLGq5rb0bUVEqLKMLnpKiA1ndkoJc8AHqxXpY0%3D&amp;req_id=20260425155845078EE3D9584F0708225B&amp;query=&amp;shop_region=ID&amp;shop_id=7495177173399997259</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-04-23T19:35:12.442257</t>
+          <t>2026-04-25T15:02:22.438386</t>
         </is>
       </c>
     </row>
